--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536316_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536316_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>D. MUNOZ SAMATAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -724,58 +724,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8802</v>
+        <v>2.9395</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7202</v>
+        <v>3.1269</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8399</v>
+        <v>-0.1873</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6857</v>
+        <v>3.4279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9054</v>
+        <v>-0.0822</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7803</v>
+        <v>3.5101</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1488</v>
+        <v>4.16</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9257</v>
+        <v>0.8855</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2231</v>
+        <v>3.2745</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4631</v>
+        <v>-0.7321</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0203</v>
+        <v>-0.9677</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4428</v>
+        <v>0.2356</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0548</v>
+        <v>-0.411</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0822</v>
+        <v>-1.2329</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0274</v>
+        <v>0.8219</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.3171</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4139</v>
+        <v>-0.0399</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4043</v>
+        <v>-0.2771</v>
       </c>
       <c r="V4" t="n">
         <v>0.2397</v>
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MUNOZ SAMATAN</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,58 +807,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3478</v>
+        <v>2.8802</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5351</v>
+        <v>3.7202</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1873</v>
+        <v>-0.8399</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8361</v>
+        <v>4.6857</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0822</v>
+        <v>0.9054</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9183</v>
+        <v>3.7803</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5682</v>
+        <v>6.1488</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8855</v>
+        <v>1.9257</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6827</v>
+        <v>4.2231</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7321</v>
+        <v>-1.4631</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9677</v>
+        <v>-1.0203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2356</v>
+        <v>-0.4428</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.411</v>
+        <v>-2.0548</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2329</v>
+        <v>-3.0822</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8219</v>
+        <v>1.0274</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3171</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0399</v>
+        <v>0.4139</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2771</v>
+        <v>-0.4043</v>
       </c>
       <c r="V5" t="n">
         <v>0.2397</v>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,58 +973,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5918</v>
+        <v>0.4734</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5918</v>
+        <v>-2.7754</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3.2488</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5918</v>
+        <v>1.0865</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.2268</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5918</v>
+        <v>0.8597</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5918</v>
+        <v>-0.7944</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.2038</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5918</v>
+        <v>-0.5906</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.4306</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.4503</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2603</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.2329</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.4143</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2794</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>A. YOUNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,64 +1056,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4734</v>
+        <v>0.2755</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7754</v>
+        <v>-1.1224</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2488</v>
+        <v>1.3979</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0865</v>
+        <v>0.6474</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2268</v>
+        <v>2.1136</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8597</v>
+        <v>-1.4662</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7944</v>
+        <v>1.0431</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2038</v>
+        <v>2.4611</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5906</v>
+        <v>-1.418</v>
       </c>
       <c r="M8" t="n">
-        <v>1.881</v>
+        <v>-0.3957</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4306</v>
+        <v>-0.3474</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4503</v>
+        <v>-0.0483</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0274</v>
+        <v>-1.6439</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2603</v>
+        <v>-3.0822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2329</v>
+        <v>1.4384</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4143</v>
+        <v>1.0322</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2794</v>
+        <v>0.677</v>
       </c>
       <c r="U8" t="n">
-        <v>0.135</v>
+        <v>0.3552</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. YOUNG</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2755</v>
+        <v>-0.4802</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1224</v>
+        <v>2.3301</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3979</v>
+        <v>-2.8103</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6474</v>
+        <v>-0.4811</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1136</v>
+        <v>-1.6959</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4662</v>
+        <v>1.2148</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0431</v>
+        <v>1.1979</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4611</v>
+        <v>-0.8542</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.418</v>
+        <v>2.0521</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3957</v>
+        <v>-1.679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3474</v>
+        <v>-0.8417</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0483</v>
+        <v>-0.8373</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6439</v>
+        <v>1.4384</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0822</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>1.4384</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0322</v>
+        <v>-0.2594</v>
       </c>
       <c r="T9" t="n">
-        <v>0.677</v>
+        <v>-0.0459</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3552</v>
+        <v>-0.2135</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2397</v>
+        <v>-1.1781</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2397</v>
+        <v>1.1781</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3561</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4802</v>
+        <v>-1.3103</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3301</v>
+        <v>-2.3488</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8103</v>
+        <v>1.0385</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4811</v>
+        <v>-2.1687</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6959</v>
+        <v>-2.7511</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2148</v>
+        <v>0.5824</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1979</v>
+        <v>-1.6464</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8542</v>
+        <v>-1.9621</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0521</v>
+        <v>0.3156</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.679</v>
+        <v>-0.5223</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8417</v>
+        <v>-0.7891</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8373</v>
+        <v>0.2668</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4384</v>
+        <v>-1.2329</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2603</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4384</v>
+        <v>1.0274</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2594</v>
+        <v>0.9132</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0459</v>
+        <v>0.3799</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2135</v>
+        <v>0.5334</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1781</v>
+        <v>1.1781</v>
       </c>
       <c r="W10" t="n">
         <v>1.1781</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3561</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3103</v>
+        <v>-2.0981</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3488</v>
+        <v>-1.1151</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0385</v>
+        <v>-0.983</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1687</v>
+        <v>-0.2603</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7511</v>
+        <v>-0.4416</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5824</v>
+        <v>0.1814</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6464</v>
+        <v>0.0395</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9621</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3156</v>
+        <v>0.0395</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5223</v>
+        <v>-0.2997</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7891</v>
+        <v>-0.4416</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2668</v>
+        <v>0.1419</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2329</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2603</v>
+        <v>-1.0274</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0274</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9132</v>
+        <v>-0.2214</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3799</v>
+        <v>-0.1271</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5334</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1781</v>
+        <v>-0.589</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0981</v>
+        <v>16.0397</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1151</v>
+        <v>14.6555</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.983</v>
+        <v>1.384300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2603</v>
+        <v>20.37769999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4416</v>
+        <v>2.312099999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1814</v>
+        <v>18.0656</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0395</v>
+        <v>23.0993</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5.9701</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0395</v>
+        <v>17.1291</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2997</v>
+        <v>-2.7213</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4416</v>
+        <v>-3.6579</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1419</v>
+        <v>0.9365</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0274</v>
+        <v>-6.1645</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0274</v>
+        <v>-16.4385</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>10.2741</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2214</v>
+        <v>2.3949</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1271</v>
+        <v>2.0841</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.3112</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.589</v>
+        <v>-0.5685999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>5.910799999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.589</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536316_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-6.4793</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>B. LIGHTBOURNE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. ZARAGOZA</t>
+          <t>BIELE ISB</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.0398</v>
+        <v>1.7321</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6555</v>
+        <v>2.6989</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3843</v>
+        <v>-0.9668</v>
       </c>
       <c r="G13" t="n">
-        <v>20.37769999999999</v>
+        <v>-0.3765</v>
       </c>
       <c r="H13" t="n">
-        <v>2.312099999999999</v>
+        <v>1.5884</v>
       </c>
       <c r="I13" t="n">
-        <v>18.0656</v>
+        <v>-1.9649</v>
       </c>
       <c r="J13" t="n">
-        <v>23.0993</v>
+        <v>1.9857</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9701</v>
+        <v>1.8674</v>
       </c>
       <c r="L13" t="n">
-        <v>17.1291</v>
+        <v>0.1184</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7213</v>
+        <v>-2.3622</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.6579</v>
+        <v>-0.2789</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9365</v>
+        <v>-2.0833</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.1645</v>
+        <v>1.2329</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.4385</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2741</v>
+        <v>1.2329</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3949</v>
+        <v>-0.1722</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0841</v>
+        <v>0.1241</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3112000000000001</v>
+        <v>-0.2964</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5685999999999998</v>
+        <v>1.048</v>
       </c>
       <c r="W13" t="n">
-        <v>5.910799999999999</v>
+        <v>0.589</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.4793</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>0.4589</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536316_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. LIGHTBOURNE</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7321</v>
+        <v>1.6905</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6989</v>
+        <v>2.5546</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9668</v>
+        <v>-0.8641</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3765</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5884</v>
+        <v>0.1729</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9649</v>
+        <v>-0.2444</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9857</v>
+        <v>1.2332</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8674</v>
+        <v>0.7197</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1184</v>
+        <v>0.5134</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3622</v>
+        <v>-1.3047</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2789</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0833</v>
+        <v>-0.7578</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2329</v>
+        <v>1.0274</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2329</v>
+        <v>1.0274</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1722</v>
+        <v>0.1456</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1241</v>
+        <v>0.1434</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2964</v>
+        <v>0.0022</v>
       </c>
       <c r="V14" t="n">
-        <v>1.048</v>
+        <v>0.589</v>
       </c>
       <c r="W14" t="n">
-        <v>0.589</v>
+        <v>1.1781</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4589</v>
+        <v>-0.589</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>S. FAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6905</v>
+        <v>0.7406</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5546</v>
+        <v>1.5609</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8641</v>
+        <v>-0.8202</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.07149999999999999</v>
+        <v>1.1099</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1729</v>
+        <v>0.8819</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2444</v>
+        <v>0.2279</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2332</v>
+        <v>2.2573</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7197</v>
+        <v>1.5866</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5134</v>
+        <v>0.6707</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3047</v>
+        <v>-1.1474</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.7047</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7578</v>
+        <v>-0.4428</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0274</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q15" t="n">
+        <v>-2.0548</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4384</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="V15" t="n">
         <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.0274</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1456</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.1434</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.589</v>
       </c>
       <c r="W15" t="n">
         <v>1.1781</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.589</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FAYE</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7406</v>
+        <v>0.3659</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5609</v>
+        <v>-0.6238</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8202</v>
+        <v>0.9897</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1099</v>
+        <v>-2.086</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8819</v>
+        <v>-0.3271</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2279</v>
+        <v>-1.7589</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2573</v>
+        <v>-0.2541</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5866</v>
+        <v>0.0203</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6707</v>
+        <v>-0.2744</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1474</v>
+        <v>-1.8319</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7047</v>
+        <v>-0.3474</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4428</v>
+        <v>-1.4844</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6163999999999999</v>
+        <v>2.4658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0548</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4384</v>
+        <v>2.4658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2472</v>
+        <v>-0.1234</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1803</v>
+        <v>-0.3697</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0669</v>
+        <v>0.2462</v>
       </c>
       <c r="V16" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.1781</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.1781</v>
+        <v>0.1096</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3659</v>
+        <v>0.1375</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6238</v>
+        <v>1.846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9897</v>
+        <v>-1.7084</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.086</v>
+        <v>-0.2915</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3271</v>
+        <v>0.6066</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7589</v>
+        <v>-0.898</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2541</v>
+        <v>2.1448</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0203</v>
+        <v>1.2745</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2744</v>
+        <v>0.8702</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8319</v>
+        <v>-2.4362</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3474</v>
+        <v>-0.668</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4844</v>
+        <v>-1.7682</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4658</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4658</v>
+        <v>1.6439</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1234</v>
+        <v>-0.7765</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3697</v>
+        <v>-0.4495</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2462</v>
+        <v>-0.327</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1096</v>
+        <v>0.589</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1781</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1096</v>
+        <v>-0.589</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>L. BADJI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1375</v>
+        <v>-1.3014</v>
       </c>
       <c r="E18" t="n">
-        <v>1.846</v>
+        <v>1.3626</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7084</v>
+        <v>-2.664</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2915</v>
+        <v>-2.8813</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6066</v>
+        <v>-0.4112</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.898</v>
+        <v>-2.4701</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1448</v>
+        <v>0.2858</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2745</v>
+        <v>0.1675</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8702</v>
+        <v>0.1184</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4362</v>
+        <v>-3.1672</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.668</v>
+        <v>-0.5787</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7682</v>
+        <v>-2.5885</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.8493</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6439</v>
+        <v>1.8493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7765</v>
+        <v>0.3196</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4495</v>
+        <v>0.4878</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.327</v>
+        <v>-0.1681</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.589</v>
+      </c>
+      <c r="W18" t="n">
         <v>0.589</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.1781</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.589</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BADJI</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3014</v>
+        <v>-1.3606</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3626</v>
+        <v>-1.7535</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.664</v>
+        <v>0.3929</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8813</v>
+        <v>-2.709</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4112</v>
+        <v>0.3682</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4701</v>
+        <v>-3.0772</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2858</v>
+        <v>-0.6771</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1675</v>
+        <v>0.6631</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1184</v>
+        <v>-1.3402</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1672</v>
+        <v>-2.0319</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5787</v>
+        <v>-0.2948</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5885</v>
+        <v>-1.737</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8493</v>
+        <v>0.2055</v>
       </c>
       <c r="Q19" t="n">
+        <v>-2.0548</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.2603</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.1996</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.8493</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3196</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.4878</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.1681</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.589</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.1781</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,40 +2048,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3606</v>
+        <v>-5.0574</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7535</v>
+        <v>-4.9709</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3929</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.709</v>
+        <v>-4.7983</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3682</v>
+        <v>-2.9753</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0772</v>
+        <v>-1.823</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6771</v>
+        <v>-2.6514</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6631</v>
+        <v>-2.0602</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3402</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0319</v>
+        <v>-2.1469</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2948</v>
+        <v>-0.9151</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.737</v>
+        <v>-1.2318</v>
       </c>
       <c r="P20" t="n">
         <v>0.2055</v>
@@ -2093,19 +2093,19 @@
         <v>2.2603</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0351</v>
+        <v>-0.4646</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1996</v>
+        <v>-0.2647</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1645</v>
+        <v>-0.1999</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1781</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>J. JERMAIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0574</v>
+        <v>-5.2666</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9709</v>
+        <v>-0.7621</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-4.5046</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.7983</v>
+        <v>-2.6949</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9753</v>
+        <v>-0.9054</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.823</v>
+        <v>-1.7895</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6514</v>
+        <v>0.8827</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0602</v>
+        <v>-0.027</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.9097</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1469</v>
+        <v>-3.5776</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9151</v>
+        <v>-0.8784</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2318</v>
+        <v>-2.6992</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2055</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.0548</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2603</v>
+        <v>1.4384</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4646</v>
+        <v>-0.1881</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2647</v>
+        <v>-0.1789</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1999</v>
+        <v>-0.0092</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.7671</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.589</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.3561</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JERMAIN</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2666</v>
+        <v>-6.3753</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7621</v>
+        <v>-3.297</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5046</v>
+        <v>-3.0783</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6949</v>
+        <v>-5.5785</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9054</v>
+        <v>-1.3112</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7895</v>
+        <v>-4.2673</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8827</v>
+        <v>-2.4854</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.027</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9097</v>
+        <v>-1.9314</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.5776</v>
+        <v>-3.0932</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8784</v>
+        <v>-0.7573</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6992</v>
+        <v>-2.3359</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4384</v>
+        <v>0.8219</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1881</v>
+        <v>-0.0022</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1789</v>
+        <v>0.2158</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0092</v>
+        <v>-0.218</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7671</v>
+        <v>-0.589</v>
       </c>
       <c r="W22" t="n">
-        <v>0.589</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3561</v>
+        <v>-0.589</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,152 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3753</v>
+        <v>-14.6947</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.297</v>
+        <v>-1.384299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0783</v>
+        <v>-13.3103</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5785</v>
+        <v>-20.3776</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3112</v>
+        <v>-2.3122</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2673</v>
+        <v>-18.0654</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4854</v>
+        <v>2.721499999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5538999999999999</v>
+        <v>3.658</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9314</v>
+        <v>-0.9364000000000003</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0932</v>
+        <v>-23.0992</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7573</v>
+        <v>-5.9702</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.3359</v>
+        <v>-17.1289</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2055</v>
+        <v>6.1645</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>-10.274</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8219</v>
+        <v>16.4386</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0022</v>
+        <v>-1.0497</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2158</v>
+        <v>-0.3109999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.218</v>
+        <v>-0.7388</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.589</v>
+        <v>0.5685999999999998</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>6.4794</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.589</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536316_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-14.6947</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1.384299999999999</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-13.3103</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-20.3776</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-2.3122</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-18.0654</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.721499999999999</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.658</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-0.9364000000000003</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-23.0992</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-5.9702</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-17.1289</v>
-      </c>
-      <c r="P24" t="n">
-        <v>6.1645</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-10.274</v>
-      </c>
-      <c r="R24" t="n">
-        <v>16.4386</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-1.0497</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-0.3109999999999999</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-0.7388</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.5685999999999998</v>
-      </c>
-      <c r="W24" t="n">
-        <v>6.4794</v>
-      </c>
-      <c r="X24" t="n">
         <v>-5.9108</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
